--- a/output_petroleo_lp_modelo9/resumo_modelo9_resultados_horizontes.xlsx
+++ b/output_petroleo_lp_modelo9/resumo_modelo9_resultados_horizontes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,7 +540,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\resumo_modelo9_resultados_horizontes.csv</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\resumo_modelo9_resultados_horizontes.csv</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\resumo_modelo9_resultados_horizontes.csv</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\resumo_modelo9_resultados_horizontes.csv</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -714,29 +714,29 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5198680877083892</v>
+        <v>0.5177904481854086</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2361559931118525</v>
+        <v>0.1221237137924591</v>
       </c>
       <c r="D6" t="n">
-        <v>2.201375797658287</v>
+        <v>4.239884557272456</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0277094309086385</v>
+        <v>2.236347678045244e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1313914790393918</v>
+        <v>0.3168969389968133</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9083446963773868</v>
+        <v>0.7186839573740039</v>
       </c>
       <c r="H6" t="n">
         <v>266</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -763,29 +763,29 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>1.080557489029402</v>
+        <v>1.186358231111196</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5424795937162589</v>
+        <v>0.3413915305364597</v>
       </c>
       <c r="D7" t="n">
-        <v>1.991885965013058</v>
+        <v>3.475066382715947</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0463835712275615</v>
+        <v>0.0005107269483612999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1881785573661559</v>
+        <v>0.6247691633787196</v>
       </c>
       <c r="G7" t="n">
-        <v>1.972936420692648</v>
+        <v>1.747947298843672</v>
       </c>
       <c r="H7" t="n">
         <v>263</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -812,29 +812,29 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.237124399051377</v>
+        <v>1.091701449039365</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7275707638089196</v>
+        <v>0.5693792608070646</v>
       </c>
       <c r="D8" t="n">
-        <v>1.70034924517154</v>
+        <v>1.917353729203162</v>
       </c>
       <c r="E8" t="n">
-        <v>0.089065252643571</v>
+        <v>0.0551930083418919</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0402704925857042</v>
+        <v>0.155072565011744</v>
       </c>
       <c r="G8" t="n">
-        <v>2.43397830551705</v>
+        <v>2.028330333066986</v>
       </c>
       <c r="H8" t="n">
         <v>260</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -861,29 +861,29 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.1588622411567457</v>
+        <v>1.084176832901811</v>
       </c>
       <c r="C9" t="n">
-        <v>1.129782450793933</v>
+        <v>0.7347347328029289</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1406131251597229</v>
+        <v>1.475603077543102</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8881755788857809</v>
+        <v>0.1400504784800293</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.017354372712765</v>
+        <v>-0.1244618025590074</v>
       </c>
       <c r="G9" t="n">
-        <v>1.699629890399274</v>
+        <v>2.292815468362629</v>
       </c>
       <c r="H9" t="n">
         <v>254</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -910,29 +910,29 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4106577116356907</v>
+        <v>0.5198680877083892</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1616179111563641</v>
+        <v>0.2361559931118525</v>
       </c>
       <c r="D10" t="n">
-        <v>2.540917084606931</v>
+        <v>2.201375797658287</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0110562135768242</v>
+        <v>0.0277094309086385</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1447962477834716</v>
+        <v>0.1313914790393918</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6765191754879097</v>
+        <v>0.9083446963773868</v>
       </c>
       <c r="H10" t="n">
         <v>266</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -959,29 +959,29 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5750432694291899</v>
+        <v>1.080557489029402</v>
       </c>
       <c r="C11" t="n">
-        <v>0.378573099324624</v>
+        <v>0.5424795937162589</v>
       </c>
       <c r="D11" t="n">
-        <v>1.518975517423371</v>
+        <v>1.991885965013058</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1287686586362435</v>
+        <v>0.0463835712275615</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0477094789598165</v>
+        <v>0.1881785573661559</v>
       </c>
       <c r="G11" t="n">
-        <v>1.197796017818197</v>
+        <v>1.972936420692648</v>
       </c>
       <c r="H11" t="n">
         <v>263</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="L11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1008,29 +1008,29 @@
         <v>6</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1746778818416606</v>
+        <v>1.237124399051377</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4666221726581549</v>
+        <v>0.7275707638089196</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3743454385088314</v>
+        <v>1.70034924517154</v>
       </c>
       <c r="E12" t="n">
-        <v>0.708147330419754</v>
+        <v>0.089065252643571</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5929155921810042</v>
+        <v>0.0402704925857042</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9422713558643256</v>
+        <v>2.43397830551705</v>
       </c>
       <c r="H12" t="n">
         <v>260</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="L12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1057,29 +1057,29 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.912545922345928</v>
+        <v>-0.1588622411567457</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7755394499817564</v>
+        <v>1.129782450793933</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.17665957852614</v>
+        <v>-0.1406131251597229</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2393314075616017</v>
+        <v>0.8881755788857809</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.188308317565917</v>
+        <v>-2.017354372712765</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3632164728740612</v>
+        <v>1.699629890399274</v>
       </c>
       <c r="H13" t="n">
         <v>254</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1106,29 +1106,29 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1827950149754326</v>
+        <v>0.4106577116356907</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1441028697558675</v>
+        <v>0.1616179111563641</v>
       </c>
       <c r="D14" t="n">
-        <v>1.268503641080262</v>
+        <v>2.540917084606931</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2046181512718626</v>
+        <v>0.0110562135768242</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0542542057729694</v>
+        <v>0.1447962477834716</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4198442357238348</v>
+        <v>0.6765191754879097</v>
       </c>
       <c r="H14" t="n">
         <v>266</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -1155,29 +1155,29 @@
         <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4572594049447334</v>
+        <v>0.5750432694291899</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4320559136056355</v>
+        <v>0.378573099324624</v>
       </c>
       <c r="D15" t="n">
-        <v>1.058333865005497</v>
+        <v>1.518975517423371</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2899032589449676</v>
+        <v>0.1287686586362435</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.253472572936537</v>
+        <v>-0.0477094789598165</v>
       </c>
       <c r="G15" t="n">
-        <v>1.167991382826004</v>
+        <v>1.197796017818197</v>
       </c>
       <c r="H15" t="n">
         <v>263</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1204,29 +1204,29 @@
         <v>6</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.1415904973738363</v>
+        <v>0.1746778818416606</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5920878816801017</v>
+        <v>0.4666221726581549</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2391376377642805</v>
+        <v>0.3743454385088314</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8109988575699456</v>
+        <v>0.708147330419754</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.115575062737604</v>
+        <v>-0.5929155921810042</v>
       </c>
       <c r="G16" t="n">
-        <v>0.832394067989931</v>
+        <v>0.9422713558643256</v>
       </c>
       <c r="H16" t="n">
         <v>260</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1253,29 +1253,29 @@
         <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.4146406338058801</v>
+        <v>-0.912545922345928</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7504264853303505</v>
+        <v>0.7755394499817564</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5525399781476906</v>
+        <v>-1.17665957852614</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5805784519604167</v>
+        <v>0.2393314075616017</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.649092202174307</v>
+        <v>-2.188308317565917</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8198109345625464</v>
+        <v>0.3632164728740612</v>
       </c>
       <c r="H17" t="n">
         <v>254</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1302,29 +1302,29 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0136763388060343</v>
+        <v>0.1827950149754326</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0186378314740408</v>
+        <v>0.1441028697558675</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7337945310366739</v>
+        <v>1.268503641080262</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4630739742191803</v>
+        <v>0.2046181512718626</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0169828939687628</v>
+        <v>-0.0542542057729694</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0443355715808315</v>
+        <v>0.4198442357238348</v>
       </c>
       <c r="H18" t="n">
         <v>266</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1351,29 +1351,29 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0865665970573489</v>
+        <v>0.4572594049447334</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0496547609416944</v>
+        <v>0.4320559136056355</v>
       </c>
       <c r="D19" t="n">
-        <v>1.743369526217174</v>
+        <v>1.058333865005497</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0812690878150876</v>
+        <v>0.2899032589449676</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0048845153082615</v>
+        <v>-0.253472572936537</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1682486788064363</v>
+        <v>1.167991382826004</v>
       </c>
       <c r="H19" t="n">
         <v>263</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -1400,29 +1400,29 @@
         <v>6</v>
       </c>
       <c r="B20" t="n">
-        <v>0.070432625703044</v>
+        <v>-0.1415904973738363</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0693359906940562</v>
+        <v>0.5920878816801017</v>
       </c>
       <c r="D20" t="n">
-        <v>1.015816244896921</v>
+        <v>-0.2391376377642805</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3097168987220444</v>
+        <v>0.8109988575699456</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0436250789886784</v>
+        <v>-1.115575062737604</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1844903303947665</v>
+        <v>0.832394067989931</v>
       </c>
       <c r="H20" t="n">
         <v>260</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1449,29 +1449,29 @@
         <v>12</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0073631598296098</v>
+        <v>-0.4146406338058801</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1075688732509164</v>
+        <v>0.7504264853303505</v>
       </c>
       <c r="D21" t="n">
-        <v>0.06845065498115251</v>
+        <v>-0.5525399781476906</v>
       </c>
       <c r="E21" t="n">
-        <v>0.945426899510118</v>
+        <v>0.5805784519604167</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1695876366681477</v>
+        <v>-1.649092202174307</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1843139563273673</v>
+        <v>0.8198109345625464</v>
       </c>
       <c r="H21" t="n">
         <v>254</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1498,29 +1498,29 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1475146344131568</v>
+        <v>0.0136763388060343</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0552998117625093</v>
+        <v>0.0186378314740408</v>
       </c>
       <c r="D22" t="n">
-        <v>2.667543156325257</v>
+        <v>0.7337945310366739</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00764080753785</v>
+        <v>0.4630739742191803</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0565464440638289</v>
+        <v>-0.0169828939687628</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2384828247624846</v>
+        <v>0.0443355715808315</v>
       </c>
       <c r="H22" t="n">
         <v>266</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -1547,29 +1547,29 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2377275005677359</v>
+        <v>0.0865665970573489</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1302133285075407</v>
+        <v>0.0496547609416944</v>
       </c>
       <c r="D23" t="n">
-        <v>1.825677166020444</v>
+        <v>1.743369526217174</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0678989046317351</v>
+        <v>0.0812690878150876</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0235265751728314</v>
+        <v>0.0048845153082615</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4519284259626404</v>
+        <v>0.1682486788064363</v>
       </c>
       <c r="H23" t="n">
         <v>263</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1596,29 +1596,29 @@
         <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1775497247018371</v>
+        <v>0.070432625703044</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1759413173711209</v>
+        <v>0.0693359906940562</v>
       </c>
       <c r="D24" t="n">
-        <v>1.009141726086565</v>
+        <v>1.015816244896921</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3129066691858565</v>
+        <v>0.3097168987220444</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1118737423736568</v>
+        <v>-0.0436250789886784</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4669731917773311</v>
+        <v>0.1844903303947665</v>
       </c>
       <c r="H24" t="n">
         <v>260</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1645,29 +1645,29 @@
         <v>12</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0627935771797471</v>
+        <v>0.0073631598296098</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2674365325964646</v>
+        <v>0.1075688732509164</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2347980530935783</v>
+        <v>0.06845065498115251</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8143654789122462</v>
+        <v>0.945426899510118</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5027266733009316</v>
+        <v>-0.1695876366681477</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3771395189414371</v>
+        <v>0.1843139563273673</v>
       </c>
       <c r="H25" t="n">
         <v>254</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1693,22 +1693,30 @@
       <c r="A26" t="n">
         <v>0</v>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>0.1475146344131568</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0552998117625093</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.667543156325257</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.00764080753785</v>
+      </c>
       <c r="F26" t="n">
-        <v>0.6074327650830804</v>
+        <v>0.0565464440638289</v>
       </c>
       <c r="G26" t="n">
-        <v>1.376982618499277</v>
+        <v>0.2384828247624846</v>
       </c>
       <c r="H26" t="n">
         <v>266</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_transporte.csv</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1716,56 +1724,48 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LP_IV</t>
+          <t>LP_direta</t>
         </is>
       </c>
       <c r="L26" t="b">
         <v>1</v>
       </c>
-      <c r="M26" t="n">
-        <v>0.9922076917911786</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.2339057305216402</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4.241912712349657</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.216228913099526e-05</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>128.3459611375896</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6.79409209403239e-24</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>2SLS_manual_aproximado</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>3</v>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0.2377275005677359</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1302133285075407</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.825677166020444</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0678989046317351</v>
+      </c>
       <c r="F27" t="n">
-        <v>1.244764667086843</v>
+        <v>0.0235265751728314</v>
       </c>
       <c r="G27" t="n">
-        <v>3.46006385117998</v>
+        <v>0.4519284259626404</v>
       </c>
       <c r="H27" t="n">
         <v>263</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_transporte.csv</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1773,56 +1773,48 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LP_IV</t>
+          <t>LP_direta</t>
         </is>
       </c>
       <c r="L27" t="b">
         <v>1</v>
       </c>
-      <c r="M27" t="n">
-        <v>2.352414259133411</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.6733432170495856</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.493633260970649</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.0004764951032705</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>126.7411545984158</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.300501702804285e-23</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>2SLS_manual_aproximado</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>6</v>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0.1775497247018371</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1759413173711209</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.009141726086565</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.3129066691858565</v>
+      </c>
       <c r="F28" t="n">
-        <v>0.4236422085587128</v>
+        <v>-0.1118737423736568</v>
       </c>
       <c r="G28" t="n">
-        <v>4.016849277740937</v>
+        <v>0.4669731917773311</v>
       </c>
       <c r="H28" t="n">
         <v>260</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_transporte.csv</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1830,56 +1822,48 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LP_IV</t>
+          <t>LP_direta</t>
         </is>
       </c>
       <c r="L28" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.220245743149825</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.092160203398852</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.032893833926853</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.0420632501388904</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>123.500833788249</v>
-      </c>
-      <c r="R28" t="n">
-        <v>4.222558706905314e-23</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>2SLS_manual_aproximado</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>12</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>-0.0627935771797471</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.2674365325964646</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.2347980530935783</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8143654789122462</v>
+      </c>
       <c r="F29" t="n">
-        <v>0.0212622542341782</v>
+        <v>-0.5027266733009316</v>
       </c>
       <c r="G29" t="n">
-        <v>4.520324471892094</v>
+        <v>0.3771395189414371</v>
       </c>
       <c r="H29" t="n">
         <v>254</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
+          <t>output_petroleo_lp_modelo9\A_lp_direta_oil_supply_news\lp_direta_acumulada_oil_supply_news_para_ipca_transporte.csv</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1887,35 +1871,19 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LP_IV</t>
+          <t>LP_direta</t>
         </is>
       </c>
       <c r="L29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.270793363063136</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.36749611478964</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.660548310524779</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.0968041975944398</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>119.2661330223113</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.157889667953848e-22</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>2SLS_manual_aproximado</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1926,17 +1894,17 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>0.3287360429225776</v>
+        <v>0.6074327650830804</v>
       </c>
       <c r="G30" t="n">
-        <v>1.801953205102732</v>
+        <v>1.376982618499277</v>
       </c>
       <c r="H30" t="n">
         <v>266</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1951,22 +1919,22 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1.065344624012655</v>
+        <v>0.9922076917911786</v>
       </c>
       <c r="N30" t="n">
-        <v>0.4477863714833294</v>
+        <v>0.2339057305216402</v>
       </c>
       <c r="O30" t="n">
-        <v>2.379135882326236</v>
+        <v>4.241912712349657</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0173532777727253</v>
+        <v>2.216228913099526e-05</v>
       </c>
       <c r="Q30" t="n">
-        <v>123.4066238634609</v>
+        <v>128.3459611375896</v>
       </c>
       <c r="R30" t="n">
-        <v>3.377142140578943e-23</v>
+        <v>6.79409209403239e-24</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -1983,17 +1951,17 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>0.5105169749926206</v>
+        <v>1.244764667086843</v>
       </c>
       <c r="G31" t="n">
-        <v>4.029510363962456</v>
+        <v>3.46006385117998</v>
       </c>
       <c r="H31" t="n">
         <v>263</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2008,22 +1976,22 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>2.270013669477538</v>
+        <v>2.352414259133411</v>
       </c>
       <c r="N31" t="n">
-        <v>1.069602853790224</v>
+        <v>0.6733432170495856</v>
       </c>
       <c r="O31" t="n">
-        <v>2.122295823569994</v>
+        <v>3.493633260970649</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0338129039854572</v>
+        <v>0.0004764951032705</v>
       </c>
       <c r="Q31" t="n">
-        <v>121.8948128838388</v>
+        <v>126.7411545984158</v>
       </c>
       <c r="R31" t="n">
-        <v>6.270318319839454e-23</v>
+        <v>1.300501702804285e-23</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -2040,17 +2008,17 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>0.3818315502845424</v>
+        <v>0.4236422085587128</v>
       </c>
       <c r="G32" t="n">
-        <v>4.884700561178258</v>
+        <v>4.016849277740937</v>
       </c>
       <c r="H32" t="n">
         <v>260</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2065,22 +2033,22 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>2.6332660557314</v>
+        <v>2.220245743149825</v>
       </c>
       <c r="N32" t="n">
-        <v>1.368653194800522</v>
+        <v>1.092160203398852</v>
       </c>
       <c r="O32" t="n">
-        <v>1.923983420880549</v>
+        <v>2.032893833926853</v>
       </c>
       <c r="P32" t="n">
-        <v>0.0543566616233684</v>
+        <v>0.0420632501388904</v>
       </c>
       <c r="Q32" t="n">
-        <v>118.5390115802745</v>
+        <v>123.500833788249</v>
       </c>
       <c r="R32" t="n">
-        <v>2.13071792073898e-22</v>
+        <v>4.222558706905314e-23</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -2097,17 +2065,17 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>-3.564550159310289</v>
+        <v>0.0212622542341782</v>
       </c>
       <c r="G33" t="n">
-        <v>3.395982241419245</v>
+        <v>4.520324471892094</v>
       </c>
       <c r="H33" t="n">
         <v>254</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_diesel.csv</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2119,25 +2087,25 @@
         </is>
       </c>
       <c r="L33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.08428395894552219</v>
+        <v>2.270793363063136</v>
       </c>
       <c r="N33" t="n">
-        <v>2.115663343686788</v>
+        <v>1.36749611478964</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.0398380768835592</v>
+        <v>1.660548310524779</v>
       </c>
       <c r="P33" t="n">
-        <v>0.96822221935105</v>
+        <v>0.0968041975944398</v>
       </c>
       <c r="Q33" t="n">
-        <v>113.8833780360036</v>
+        <v>119.2661330223113</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25758824953858e-21</v>
+        <v>2.157889667953848e-22</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -2154,17 +2122,17 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.3138920661793691</v>
+        <v>0.3287360429225776</v>
       </c>
       <c r="G34" t="n">
-        <v>1.318784893324733</v>
+        <v>1.801953205102732</v>
       </c>
       <c r="H34" t="n">
         <v>266</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2179,22 +2147,22 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8163384797520509</v>
+        <v>1.065344624012655</v>
       </c>
       <c r="N34" t="n">
-        <v>0.3054385492843049</v>
+        <v>0.4477863714833294</v>
       </c>
       <c r="O34" t="n">
-        <v>2.672676653503208</v>
+        <v>2.379135882326236</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0075248743170519</v>
+        <v>0.0173532777727253</v>
       </c>
       <c r="Q34" t="n">
-        <v>124.6951308196308</v>
+        <v>123.4066238634609</v>
       </c>
       <c r="R34" t="n">
-        <v>2.217777391640481e-23</v>
+        <v>3.377142140578943e-23</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -2211,17 +2179,17 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>0.014691726633879</v>
+        <v>0.5105169749926206</v>
       </c>
       <c r="G35" t="n">
-        <v>2.401104438444179</v>
+        <v>4.029510363962456</v>
       </c>
       <c r="H35" t="n">
         <v>263</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2236,22 +2204,22 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>1.207898082539029</v>
+        <v>2.270013669477538</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7253534078450758</v>
+        <v>1.069602853790224</v>
       </c>
       <c r="O35" t="n">
-        <v>1.665254577251558</v>
+        <v>2.122295823569994</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0958619765361837</v>
+        <v>0.0338129039854572</v>
       </c>
       <c r="Q35" t="n">
-        <v>123.1874191502729</v>
+        <v>121.8948128838388</v>
       </c>
       <c r="R35" t="n">
-        <v>4.112676417326383e-23</v>
+        <v>6.270318319839454e-23</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -2268,17 +2236,17 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>-1.005116268895598</v>
+        <v>0.3818315502845424</v>
       </c>
       <c r="G36" t="n">
-        <v>1.86844719215659</v>
+        <v>4.884700561178258</v>
       </c>
       <c r="H36" t="n">
         <v>260</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2290,25 +2258,25 @@
         </is>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4316654616304961</v>
+        <v>2.6332660557314</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8734235443927624</v>
+        <v>1.368653194800522</v>
       </c>
       <c r="O36" t="n">
-        <v>0.4942223785948048</v>
+        <v>1.923983420880549</v>
       </c>
       <c r="P36" t="n">
-        <v>0.62114913689827</v>
+        <v>0.0543566616233684</v>
       </c>
       <c r="Q36" t="n">
-        <v>119.8052677097702</v>
+        <v>118.5390115802745</v>
       </c>
       <c r="R36" t="n">
-        <v>1.406509780257039e-22</v>
+        <v>2.13071792073898e-22</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -2325,17 +2293,17 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>-3.91811609587263</v>
+        <v>-3.564550159310289</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8081677802347078</v>
+        <v>3.395982241419245</v>
       </c>
       <c r="H37" t="n">
         <v>254</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_etanol.csv</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2350,22 +2318,22 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.554974157818961</v>
+        <v>-0.08428395894552219</v>
       </c>
       <c r="N37" t="n">
-        <v>1.436560448664844</v>
+        <v>2.115663343686788</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.08242862962305</v>
+        <v>-0.0398380768835592</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2790621125591832</v>
+        <v>0.96822221935105</v>
       </c>
       <c r="Q37" t="n">
-        <v>115.1965913828036</v>
+        <v>113.8833780360036</v>
       </c>
       <c r="R37" t="n">
-        <v>8.158436602333592e-22</v>
+        <v>1.25758824953858e-21</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -2382,17 +2350,17 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>-0.095857420947891</v>
+        <v>0.3138920661793691</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8275542738573347</v>
+        <v>1.318784893324733</v>
       </c>
       <c r="H38" t="n">
         <v>266</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -2404,25 +2372,25 @@
         </is>
       </c>
       <c r="L38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3658484264547218</v>
+        <v>0.8163384797520509</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2806722476611628</v>
+        <v>0.3054385492843049</v>
       </c>
       <c r="O38" t="n">
-        <v>1.303472037236779</v>
+        <v>2.672676653503208</v>
       </c>
       <c r="P38" t="n">
-        <v>0.192413656864731</v>
+        <v>0.0075248743170519</v>
       </c>
       <c r="Q38" t="n">
-        <v>125.6862316210125</v>
+        <v>124.6951308196308</v>
       </c>
       <c r="R38" t="n">
-        <v>1.606585218056111e-23</v>
+        <v>2.217777391640481e-23</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -2439,17 +2407,17 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>-0.4822751113392808</v>
+        <v>0.014691726633879</v>
       </c>
       <c r="G39" t="n">
-        <v>2.301593406548132</v>
+        <v>2.401104438444179</v>
       </c>
       <c r="H39" t="n">
         <v>263</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2461,25 +2429,25 @@
         </is>
       </c>
       <c r="L39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9096591476044256</v>
+        <v>1.207898082539029</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8461606437347758</v>
+        <v>0.7253534078450758</v>
       </c>
       <c r="O39" t="n">
-        <v>1.075043083532437</v>
+        <v>1.665254577251558</v>
       </c>
       <c r="P39" t="n">
-        <v>0.282355439738205</v>
+        <v>0.0958619765361837</v>
       </c>
       <c r="Q39" t="n">
-        <v>124.1501441424754</v>
+        <v>123.1874191502729</v>
       </c>
       <c r="R39" t="n">
-        <v>3.007151488416594e-23</v>
+        <v>4.112676417326383e-23</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -2496,17 +2464,17 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>-2.005518642503212</v>
+        <v>-1.005116268895598</v>
       </c>
       <c r="G40" t="n">
-        <v>1.658510821143704</v>
+        <v>1.86844719215659</v>
       </c>
       <c r="H40" t="n">
         <v>260</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2521,22 +2489,22 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.1735039106797537</v>
+        <v>0.4316654616304961</v>
       </c>
       <c r="N40" t="n">
-        <v>1.113686767065932</v>
+        <v>0.8734235443927624</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.1557923788004226</v>
+        <v>0.4942223785948048</v>
       </c>
       <c r="P40" t="n">
-        <v>0.8761966781106439</v>
+        <v>0.62114913689827</v>
       </c>
       <c r="Q40" t="n">
-        <v>120.6950597786472</v>
+        <v>119.8052677097702</v>
       </c>
       <c r="R40" t="n">
-        <v>1.051469646147658e-22</v>
+        <v>1.406509780257039e-22</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -2553,17 +2521,17 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>-2.858016650776301</v>
+        <v>-3.91811609587263</v>
       </c>
       <c r="G41" t="n">
-        <v>1.637648673467694</v>
+        <v>0.8081677802347078</v>
       </c>
       <c r="H41" t="n">
         <v>254</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina.csv</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2578,22 +2546,22 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.6101839886543038</v>
+        <v>-1.554974157818961</v>
       </c>
       <c r="N41" t="n">
-        <v>1.366463624390272</v>
+        <v>1.436560448664844</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.4465424309604825</v>
+        <v>-1.08242862962305</v>
       </c>
       <c r="P41" t="n">
-        <v>0.6552054698454048</v>
+        <v>0.2790621125591832</v>
       </c>
       <c r="Q41" t="n">
-        <v>115.9090079177726</v>
+        <v>115.1965913828036</v>
       </c>
       <c r="R41" t="n">
-        <v>6.456144984636169e-22</v>
+        <v>8.158436602333592e-22</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -2610,17 +2578,17 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>-0.0316413148804101</v>
+        <v>-0.095857420947891</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0881633092969641</v>
+        <v>0.8275542738573347</v>
       </c>
       <c r="H42" t="n">
         <v>266</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2635,22 +2603,22 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.028260997208277</v>
+        <v>0.3658484264547218</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0364147793852201</v>
+        <v>0.2806722476611628</v>
       </c>
       <c r="O42" t="n">
-        <v>0.7760859103199028</v>
+        <v>1.303472037236779</v>
       </c>
       <c r="P42" t="n">
-        <v>0.4376982622667804</v>
+        <v>0.192413656864731</v>
       </c>
       <c r="Q42" t="n">
-        <v>127.3226784720803</v>
+        <v>125.6862316210125</v>
       </c>
       <c r="R42" t="n">
-        <v>9.453559557433268e-24</v>
+        <v>1.606585218056111e-23</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -2667,17 +2635,17 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>0.008178186861903599</v>
+        <v>-0.4822751113392808</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3336793080042475</v>
+        <v>2.301593406548132</v>
       </c>
       <c r="H43" t="n">
         <v>263</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2689,25 +2657,25 @@
         </is>
       </c>
       <c r="L43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1709287474330756</v>
+        <v>0.9096591476044256</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0989365109855148</v>
+        <v>0.8461606437347758</v>
       </c>
       <c r="O43" t="n">
-        <v>1.727660958835521</v>
+        <v>1.075043083532437</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0840490268896003</v>
+        <v>0.282355439738205</v>
       </c>
       <c r="Q43" t="n">
-        <v>125.4303813892021</v>
+        <v>124.1501441424754</v>
       </c>
       <c r="R43" t="n">
-        <v>1.985796547639876e-23</v>
+        <v>3.007151488416594e-23</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -2724,17 +2692,17 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>-0.07610301482604449</v>
+        <v>-2.005518642503212</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3687001637559387</v>
+        <v>1.658510821143704</v>
       </c>
       <c r="H44" t="n">
         <v>260</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2749,22 +2717,22 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1462985744649471</v>
+        <v>-0.1735039106797537</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1351985345233991</v>
+        <v>1.113686767065932</v>
       </c>
       <c r="O44" t="n">
-        <v>1.082101777069387</v>
+        <v>-0.1557923788004226</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2792073062755742</v>
+        <v>0.8761966781106439</v>
       </c>
       <c r="Q44" t="n">
-        <v>122.8578711897179</v>
+        <v>120.6950597786472</v>
       </c>
       <c r="R44" t="n">
-        <v>5.200933773108416e-23</v>
+        <v>1.051469646147658e-22</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -2781,17 +2749,17 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>-0.3093110897372541</v>
+        <v>-2.858016650776301</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3768213442678746</v>
+        <v>1.637648673467694</v>
       </c>
       <c r="H45" t="n">
         <v>254</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_gasolina_refinaria.csv</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2806,22 +2774,22 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0337551272653102</v>
+        <v>-0.6101839886543038</v>
       </c>
       <c r="N45" t="n">
-        <v>0.2085508917948719</v>
+        <v>1.366463624390272</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1618555882202191</v>
+        <v>-0.4465424309604825</v>
       </c>
       <c r="P45" t="n">
-        <v>0.8714195770375073</v>
+        <v>0.6552054698454048</v>
       </c>
       <c r="Q45" t="n">
-        <v>118.1142271048735</v>
+        <v>115.9090079177726</v>
       </c>
       <c r="R45" t="n">
-        <v>3.138953543436554e-22</v>
+        <v>6.456144984636169e-22</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -2838,17 +2806,17 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>0.1151851083701398</v>
+        <v>-0.0316413148804101</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4718991646020849</v>
+        <v>0.0881633092969641</v>
       </c>
       <c r="H46" t="n">
         <v>266</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2860,25 +2828,25 @@
         </is>
       </c>
       <c r="L46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2935421364861124</v>
+        <v>0.028260997208277</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1084237252984635</v>
+        <v>0.0364147793852201</v>
       </c>
       <c r="O46" t="n">
-        <v>2.707360733806774</v>
+        <v>0.7760859103199028</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0067820519157392</v>
+        <v>0.4376982622667804</v>
       </c>
       <c r="Q46" t="n">
-        <v>128.719032927988</v>
+        <v>127.3226784720803</v>
       </c>
       <c r="R46" t="n">
-        <v>6.024644836721237e-24</v>
+        <v>9.453559557433268e-24</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -2895,17 +2863,17 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>0.075091511292854</v>
+        <v>0.008178186861903599</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9172671845264726</v>
+        <v>0.3336793080042475</v>
       </c>
       <c r="H47" t="n">
         <v>263</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2920,22 +2888,22 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4961793479096633</v>
+        <v>0.1709287474330756</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2559804477913734</v>
+        <v>0.0989365109855148</v>
       </c>
       <c r="O47" t="n">
-        <v>1.938348620727683</v>
+        <v>1.727660958835521</v>
       </c>
       <c r="P47" t="n">
-        <v>0.0525807042911696</v>
+        <v>0.0840490268896003</v>
       </c>
       <c r="Q47" t="n">
-        <v>126.9954094119917</v>
+        <v>125.4303813892021</v>
       </c>
       <c r="R47" t="n">
-        <v>1.198215792226263e-23</v>
+        <v>1.985796547639876e-23</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -2952,17 +2920,17 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>-0.1676638315012729</v>
+        <v>-0.07610301482604449</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9395826400374508</v>
+        <v>0.3687001637559387</v>
       </c>
       <c r="H48" t="n">
         <v>260</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2977,22 +2945,22 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3859594042680889</v>
+        <v>0.1462985744649471</v>
       </c>
       <c r="N48" t="n">
-        <v>0.3365490794950527</v>
+        <v>0.1351985345233991</v>
       </c>
       <c r="O48" t="n">
-        <v>1.146814618679599</v>
+        <v>1.082101777069387</v>
       </c>
       <c r="P48" t="n">
-        <v>0.2514582460722737</v>
+        <v>0.2792073062755742</v>
       </c>
       <c r="Q48" t="n">
-        <v>123.2344036952497</v>
+        <v>122.8578711897179</v>
       </c>
       <c r="R48" t="n">
-        <v>4.603184861434509e-23</v>
+        <v>5.200933773108416e-23</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -3009,17 +2977,17 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>-0.8790459858786129</v>
+        <v>-0.3093110897372541</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7955203231307101</v>
+        <v>0.3768213442678746</v>
       </c>
       <c r="H49" t="n">
         <v>254</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_geral.csv</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3034,24 +3002,252 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
+        <v>0.0337551272653102</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.2085508917948719</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.1618555882202191</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.8714195770375073</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>118.1142271048735</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3.138953543436554e-22</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2SLS_manual_aproximado</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>0.1151851083701398</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.4718991646020849</v>
+      </c>
+      <c r="H50" t="n">
+        <v>266</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>LP_IV</t>
+        </is>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.2935421364861124</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.1084237252984635</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2.707360733806774</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.0067820519157392</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>128.719032927988</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6.024644836721237e-24</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2SLS_manual_aproximado</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>0.075091511292854</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.9172671845264726</v>
+      </c>
+      <c r="H51" t="n">
+        <v>263</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>LP_IV</t>
+        </is>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.4961793479096633</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.2559804477913734</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.938348620727683</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.0525807042911696</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>126.9954094119917</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.198215792226263e-23</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2SLS_manual_aproximado</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>-0.1676638315012729</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.9395826400374508</v>
+      </c>
+      <c r="H52" t="n">
+        <v>260</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>6</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>LP_IV</t>
+        </is>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.3859594042680889</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.3365490794950527</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.146814618679599</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.2514582460722737</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>123.2344036952497</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4.603184861434509e-23</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2SLS_manual_aproximado</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>12</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>-0.8790459858786129</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.7955203231307101</v>
+      </c>
+      <c r="H53" t="n">
+        <v>254</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>output_petroleo_lp_modelo9\B_lpiv_oil_supply_news\lpiv_acumulada_petroleo_brl_iv_oil_supply_news_para_ipca_transporte.csv</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>12</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>LP_IV</t>
+        </is>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>-0.0417628313739513</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N53" t="n">
         <v>0.508986720063624</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O53" t="n">
         <v>-0.0820509253536732</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P53" t="n">
         <v>0.934606217365565</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q53" t="n">
         <v>118.8751750973308</v>
       </c>
-      <c r="R49" t="n">
+      <c r="R53" t="n">
         <v>2.450216510222392e-22</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>2SLS_manual_aproximado</t>
         </is>
